--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_43.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3586026.958259153</v>
+        <v>3622385.004566367</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337384</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337384</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117083683</v>
+        <v>603.5370117055771</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117083683</v>
+        <v>603.5370117055771</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>284.0866125145364</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
@@ -799,7 +799,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>170.2973659882994</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>6.161977474695165</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -909,7 +909,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>104.7151487679343</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>374</v>
+        <v>141.2717495919814</v>
       </c>
       <c r="V6" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1146,10 +1146,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1270,13 +1270,13 @@
         <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>105.5644631017525</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>302.117790950501</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1444,22 +1444,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>116.6353649945384</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H12" t="n">
         <v>4.021973978873973</v>
@@ -1507,7 +1507,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>206.3364106824544</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
@@ -1617,7 +1617,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>195.2639131038855</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>113.599510110503</v>
       </c>
       <c r="G15" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,22 +1726,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1802,13 +1802,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S16" t="n">
         <v>30.56285675203577</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S17" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T17" t="n">
         <v>259.6218731858503</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
@@ -1927,10 +1927,10 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1939,7 +1939,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>173.591815881973</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>284.9649587918013</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>317.3734759809475</v>
+        <v>317.8340633462618</v>
       </c>
       <c r="X20" t="n">
         <v>271.2818334606677</v>
@@ -2167,13 +2167,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,19 +2200,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499106</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
         <v>414.5106671915202</v>
@@ -2221,7 +2221,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2443,22 +2443,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>98.86273944538755</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -2644,13 +2644,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>306.940513035463</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
         <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2759,7 +2759,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,13 +2802,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>237.1483725282995</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
         <v>3.99961134672543</v>
@@ -3169,10 +3169,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3230,7 +3230,7 @@
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S34" t="n">
         <v>30.56285675203577</v>
@@ -3279,10 +3279,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274924</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>3.999611346725456</v>
@@ -3403,10 +3403,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3470,7 +3470,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090246903</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>18.63624233787687</v>
@@ -3637,7 +3637,7 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>267.1024830734935</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>111.3731429098285</v>
@@ -3646,7 +3646,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>251.9832086481073</v>
       </c>
     </row>
     <row r="40">
@@ -3753,7 +3753,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3817,13 +3817,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -3835,7 +3835,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>483.2744725660229</v>
       </c>
       <c r="S42" t="n">
         <v>131.8202263797056</v>
@@ -3871,7 +3871,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>252.7534963968768</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090251496</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>237.1483725282997</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,22 +4099,22 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>111.3731429098285</v>
+        <v>284.9649587918018</v>
       </c>
       <c r="X45" t="n">
         <v>98.86273944538755</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,13 +4172,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,49 +4297,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>886.1402453266331</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4424,22 +4424,22 @@
         <v>1492.786030368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1357.784024336592</v>
+        <v>1205.829856111428</v>
       </c>
       <c r="S3" t="n">
-        <v>1294.664012937232</v>
+        <v>1142.709844712069</v>
       </c>
       <c r="T3" t="n">
-        <v>1290.14538216673</v>
+        <v>1138.191213941567</v>
       </c>
       <c r="U3" t="n">
-        <v>1289.947477320344</v>
+        <v>1137.99330909518</v>
       </c>
       <c r="V3" t="n">
-        <v>1275.29023773295</v>
+        <v>1123.336069507786</v>
       </c>
       <c r="W3" t="n">
-        <v>1242.590093379587</v>
+        <v>1090.635925154424</v>
       </c>
       <c r="X3" t="n">
         <v>1070.572551977265</v>
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1021.390865612444</v>
+        <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>1147.39287143088</v>
+        <v>155.9220058184358</v>
       </c>
       <c r="D4" t="n">
-        <v>1260.71201555588</v>
+        <v>269.2411499434359</v>
       </c>
       <c r="E4" t="n">
-        <v>1378.540919767293</v>
+        <v>387.0700541548489</v>
       </c>
       <c r="F4" t="n">
-        <v>1378.540919767293</v>
+        <v>511.4310267467844</v>
       </c>
       <c r="G4" t="n">
-        <v>1382.983127881912</v>
+        <v>511.4310267467844</v>
       </c>
       <c r="H4" t="n">
-        <v>1382.983127881912</v>
+        <v>682.5666027258541</v>
       </c>
       <c r="I4" t="n">
-        <v>1382.983127881912</v>
+        <v>909.175577399642</v>
       </c>
       <c r="J4" t="n">
-        <v>1382.983127881912</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4512,19 +4512,19 @@
         <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="V4" t="n">
-        <v>475.302517983249</v>
+        <v>29.92</v>
       </c>
       <c r="W4" t="n">
-        <v>647.1934362429264</v>
+        <v>29.92</v>
       </c>
       <c r="X4" t="n">
-        <v>798.2242272671199</v>
+        <v>29.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>909.6335279461522</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="5">
@@ -4543,13 +4543,13 @@
         <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4561,22 +4561,22 @@
         <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L5" t="n">
-        <v>464.2419149748744</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>451.8183303517588</v>
       </c>
       <c r="N5" t="n">
-        <v>1204.761914974874</v>
+        <v>451.8183303517588</v>
       </c>
       <c r="O5" t="n">
-        <v>1204.761914974874</v>
+        <v>755.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1262.853806841132</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4658,19 +4658,19 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1387.013152825168</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1252.011146793224</v>
+        <v>968.469334165078</v>
       </c>
       <c r="S6" t="n">
-        <v>1188.891135393864</v>
+        <v>590.6915563873001</v>
       </c>
       <c r="T6" t="n">
-        <v>1184.372504623362</v>
+        <v>586.1729256167982</v>
       </c>
       <c r="U6" t="n">
-        <v>806.5947268455845</v>
+        <v>443.4741886552009</v>
       </c>
       <c r="V6" t="n">
         <v>428.8169490678068</v>
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.92</v>
+        <v>482.3640358769909</v>
       </c>
       <c r="C7" t="n">
-        <v>29.92</v>
+        <v>482.3640358769909</v>
       </c>
       <c r="D7" t="n">
-        <v>143.2391441250001</v>
+        <v>482.3640358769909</v>
       </c>
       <c r="E7" t="n">
-        <v>261.0680483364131</v>
+        <v>600.1929400884039</v>
       </c>
       <c r="F7" t="n">
-        <v>385.4290209283486</v>
+        <v>724.5539126803394</v>
       </c>
       <c r="G7" t="n">
-        <v>487.2184261700831</v>
+        <v>878.1425736491919</v>
       </c>
       <c r="H7" t="n">
-        <v>658.3540021491528</v>
+        <v>1049.278149628262</v>
       </c>
       <c r="I7" t="n">
-        <v>884.9629768229406</v>
+        <v>1275.887124302049</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.222976822941</v>
+        <v>1275.887124302049</v>
       </c>
       <c r="K7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="Y7" t="n">
-        <v>29.92</v>
+        <v>370.6066982106988</v>
       </c>
     </row>
     <row r="8">
@@ -4789,31 +4789,31 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>145.6202453266332</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M8" t="n">
-        <v>515.8802453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>697.388108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4895,28 +4895,28 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1143.408558894664</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V9" t="n">
-        <v>765.6307811168861</v>
+        <v>912.1696995425659</v>
       </c>
       <c r="W9" t="n">
-        <v>732.9306367635239</v>
+        <v>805.5389287327149</v>
       </c>
       <c r="X9" t="n">
-        <v>712.8672635863647</v>
+        <v>785.4755555555557</v>
       </c>
       <c r="Y9" t="n">
         <v>407.6977777777778</v>
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>353.8993100962325</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C10" t="n">
-        <v>479.9013159146683</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D10" t="n">
-        <v>593.2204600396684</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E10" t="n">
-        <v>711.0493642510814</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F10" t="n">
-        <v>835.4103368430169</v>
+        <v>1057.51937437598</v>
       </c>
       <c r="G10" t="n">
-        <v>988.9989978118695</v>
+        <v>1211.108035344832</v>
       </c>
       <c r="H10" t="n">
-        <v>1160.134573790939</v>
+        <v>1382.243611323902</v>
       </c>
       <c r="I10" t="n">
         <v>1386.743548464727</v>
@@ -4995,10 +4995,10 @@
         <v>201.8109182596774</v>
       </c>
       <c r="X10" t="n">
-        <v>201.8109182596774</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y10" t="n">
-        <v>242.1419724299404</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="11">
@@ -5035,19 +5035,19 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>949.6332762537361</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M11" t="n">
-        <v>1592.143276253736</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="N11" t="n">
-        <v>1792.359898617045</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.937701241021</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C12" t="n">
-        <v>776.43273917484</v>
+        <v>872.3552318744619</v>
       </c>
       <c r="D12" t="n">
-        <v>424.9805301872616</v>
+        <v>520.9030228868835</v>
       </c>
       <c r="E12" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G12" t="n">
         <v>55.98259997866058</v>
@@ -5150,13 +5150,13 @@
         <v>1592.843862392842</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.423245541878</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.561892566739</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.378667550442</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="13">
@@ -5257,7 +5257,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G14" t="n">
         <v>125.5027119537179</v>
@@ -5272,13 +5272,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L14" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1592.599638490728</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="N14" t="n">
         <v>1756.89799366138</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>668.0405455662462</v>
+        <v>588.6177696982191</v>
       </c>
       <c r="C15" t="n">
-        <v>303.2931592576409</v>
+        <v>548.1128076320381</v>
       </c>
       <c r="D15" t="n">
-        <v>276.0833745124867</v>
+        <v>196.6605986444596</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>174.7695913495984</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R15" t="n">
-        <v>2062.032218270268</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>1038.814233293368</v>
       </c>
       <c r="V15" t="n">
-        <v>1348.024214018445</v>
+        <v>944.3590139079939</v>
       </c>
       <c r="W15" t="n">
-        <v>1235.526089867103</v>
+        <v>831.860889756652</v>
       </c>
       <c r="X15" t="n">
-        <v>1135.664736891964</v>
+        <v>731.999536781513</v>
       </c>
       <c r="Y15" t="n">
-        <v>1056.481511875667</v>
+        <v>652.8163117652157</v>
       </c>
     </row>
     <row r="16">
@@ -5448,7 +5448,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R16" t="n">
         <v>82.79157247680381</v>
@@ -5506,31 +5506,31 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>1417.990475851726</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M17" t="n">
-        <v>2060.500475851726</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N17" t="n">
-        <v>2238.277892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>2222.086939471673</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2418.678945810293</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S17" t="n">
         <v>2451.762030971221</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C18" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D18" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E18" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F18" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G18" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463101</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>227.2652685676495</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5624,13 +5624,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X18" t="n">
-        <v>960.3194683243149</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y18" t="n">
-        <v>556.8938190655933</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="19">
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D20" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H20" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
@@ -5746,22 +5746,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.599638490728</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5779,16 +5779,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W20" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5843,16 +5843,16 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R21" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U21" t="n">
         <v>1591.376589078594</v>
@@ -5864,10 +5864,10 @@
         <v>735.9383970570298</v>
       </c>
       <c r="X21" t="n">
-        <v>311.8346198394665</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.6513948231691</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5989,13 +5989,13 @@
         <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>1166.141587033441</v>
+        <v>563.4049796447796</v>
       </c>
       <c r="N23" t="n">
-        <v>1170.453074689115</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O23" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P23" t="n">
         <v>2009.555081027735</v>
@@ -6016,16 +6016,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W23" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1237.102618183067</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6092,19 +6092,19 @@
         <v>1767.260375227614</v>
       </c>
       <c r="U24" t="n">
-        <v>1687.299081778216</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V24" t="n">
-        <v>1592.843862392842</v>
+        <v>944.3590139079936</v>
       </c>
       <c r="W24" t="n">
-        <v>1480.3457382415</v>
+        <v>507.6184655142274</v>
       </c>
       <c r="X24" t="n">
-        <v>1380.484385266361</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y24" t="n">
-        <v>1301.301160250064</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6223,10 +6223,10 @@
         <v>1201.938527309012</v>
       </c>
       <c r="L26" t="n">
-        <v>1417.990475851726</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M26" t="n">
-        <v>1417.990475851726</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N26" t="n">
         <v>1651.83297330616</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1316.525394051095</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C27" t="n">
-        <v>1276.020431984914</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D27" t="n">
-        <v>1248.81064723976</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E27" t="n">
-        <v>902.6772157024741</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F27" t="n">
-        <v>559.6103042500731</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6338,10 +6338,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y27" t="n">
-        <v>1380.723936118092</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
@@ -6457,13 +6457,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.599638490728</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N29" t="n">
         <v>1651.83297330616</v>
@@ -6478,28 +6478,28 @@
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.180125483445</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C30" t="n">
         <v>776.43273917484</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872616</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R30" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S30" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U30" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V30" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W30" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X30" t="n">
-        <v>1459.907161134389</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y30" t="n">
-        <v>1380.723936118091</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="31">
@@ -6618,25 +6618,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6691,25 +6691,25 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1166.141587033441</v>
+        <v>1149.849898617045</v>
       </c>
       <c r="N32" t="n">
-        <v>1205.91497964478</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O32" t="n">
-        <v>1367.045081027735</v>
+        <v>1953.49</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F33" t="n">
         <v>60.0226114399994</v>
@@ -6812,10 +6812,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="34">
@@ -6858,19 +6858,19 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R34" t="n">
         <v>82.79157247680381</v>
@@ -6922,7 +6922,7 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6931,22 +6931,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="O35" t="n">
-        <v>1812.963074689115</v>
+        <v>2060.500475851726</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2257.092482190346</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>343.7981213238222</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C36" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D36" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E36" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
         <v>60.02261143999941</v>
@@ -7046,13 +7046,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>811.4223126495403</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>732.239087633243</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7086,31 +7086,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611898</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024176</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405787</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468619</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605517</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111728</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645522</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881906</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949744347</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7165,25 +7165,25 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>492.6952769985968</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C39" t="n">
-        <v>127.9478906899915</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D39" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E39" t="n">
         <v>78.84709864997603</v>
@@ -7280,16 +7280,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>1284.561892566739</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y39" t="n">
-        <v>881.1362433080176</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="40">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,49 +7405,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>991.9887866314309</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M41" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>2238.277892278425</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O41" t="n">
-        <v>2399.40799366138</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2166.373694755016</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>686.2820590119658</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D42" t="n">
-        <v>749.2229544296858</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1622.879563655678</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1540.682240298937</v>
       </c>
       <c r="U42" t="n">
-        <v>1591.376589078594</v>
+        <v>1136.478522607115</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1042.023303221741</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>929.5251790703986</v>
       </c>
       <c r="X42" t="n">
-        <v>1284.561892566739</v>
+        <v>829.6638260952597</v>
       </c>
       <c r="Y42" t="n">
-        <v>1205.378667550442</v>
+        <v>750.4806010789623</v>
       </c>
     </row>
     <row r="43">
@@ -7542,49 +7542,49 @@
         <v>734.4361027208327</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468458327</v>
+        <v>769.5452468459098</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510572457</v>
+        <v>809.1641510573228</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236492582</v>
       </c>
       <c r="G43" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141263074</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187344</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434903</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611944</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024223</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405833</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468666</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605563</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111774</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645985</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425882369</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949748986</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7627,7 +7627,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
         <v>125.5027119537179</v>
@@ -7639,22 +7639,22 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L44" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M44" t="n">
-        <v>1166.141587033441</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N44" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P44" t="n">
         <v>2009.555081027735</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C45" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E45" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7742,28 +7742,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1280.395625967535</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095642</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W45" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X45" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y45" t="n">
-        <v>1380.723936118092</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="46">
@@ -7815,10 +7815,10 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>184.5002908654719</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,25 +8204,25 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>307.8879745433834</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q5" t="n">
-        <v>364.0430754681111</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>720.3111720492747</v>
       </c>
       <c r="N8" t="n">
-        <v>587.423942175285</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,22 +8678,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N11" t="n">
-        <v>432.7310660354131</v>
+        <v>628.2994929102651</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>23.48346824708341</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L14" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>643.3042832636559</v>
       </c>
       <c r="N14" t="n">
-        <v>396.4499880630329</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>486.2423218353989</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>410.0652014529786</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>202.5956441962828</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,13 +9389,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>318.9437086192779</v>
       </c>
       <c r="N20" t="n">
         <v>879.4920535472222</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9632,16 +9632,16 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>950.4344291498551</v>
+        <v>341.6095732017122</v>
       </c>
       <c r="N23" t="n">
-        <v>234.8470915832563</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9866,13 +9866,13 @@
         <v>473.08808040201</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M26" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
-        <v>466.6965964304885</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>290.3237048759414</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>950.4344291498551</v>
+        <v>503.6734416380457</v>
       </c>
       <c r="N32" t="n">
-        <v>270.6671975990795</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>450.422215819576</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N35" t="n">
-        <v>290.7846768324985</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>365.8142943174411</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>950.4344291498551</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,13 +11048,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>911.3123136417682</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
         <v>879.4920535472222</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>457.4494331410071</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,16 +11291,16 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N44" t="n">
-        <v>721.0894134186553</v>
+        <v>489.3624610129226</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8382458495976817</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495667287</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495208098</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26281,37 +26281,37 @@
         <v>1353808.691614621</v>
       </c>
       <c r="F2" t="n">
-        <v>1353808.691614621</v>
+        <v>1353808.69161462</v>
       </c>
       <c r="G2" t="n">
         <v>1353808.691614621</v>
       </c>
       <c r="H2" t="n">
+        <v>1353808.69161462</v>
+      </c>
+      <c r="I2" t="n">
         <v>1353808.691614621</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1353808.69161462</v>
       </c>
       <c r="J2" t="n">
         <v>1353808.69161462</v>
       </c>
       <c r="K2" t="n">
-        <v>1353808.691614621</v>
+        <v>1353808.69161462</v>
       </c>
       <c r="L2" t="n">
         <v>1353808.691614621</v>
       </c>
       <c r="M2" t="n">
+        <v>1353808.69161462</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1353808.69161462</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1353808.691614622</v>
+      </c>
+      <c r="P2" t="n">
         <v>1353808.691614621</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1353808.691614619</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1353808.69161462</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1353808.69161462</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462996</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497198</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301401</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>486676.9836907744</v>
+        <v>493178.3486237513</v>
       </c>
       <c r="C6" t="n">
-        <v>719783.9058782632</v>
+        <v>726285.2708112402</v>
       </c>
       <c r="D6" t="n">
-        <v>721795.5532940868</v>
+        <v>728296.9182270636</v>
       </c>
       <c r="E6" t="n">
-        <v>200375.1628184459</v>
+        <v>206838.1539487999</v>
       </c>
       <c r="F6" t="n">
-        <v>791611.2256366686</v>
+        <v>798074.216767022</v>
       </c>
       <c r="G6" t="n">
-        <v>793299.6151583219</v>
+        <v>799762.6062886757</v>
       </c>
       <c r="H6" t="n">
-        <v>794990.3480682845</v>
+        <v>801453.3391986378</v>
       </c>
       <c r="I6" t="n">
-        <v>796683.441268831</v>
+        <v>803146.4323991862</v>
       </c>
       <c r="J6" t="n">
-        <v>409930.9118837559</v>
+        <v>416393.9030141099</v>
       </c>
       <c r="K6" t="n">
-        <v>800076.7772625899</v>
+        <v>806539.7683929434</v>
       </c>
       <c r="L6" t="n">
-        <v>801777.0549849343</v>
+        <v>808240.046115288</v>
       </c>
       <c r="M6" t="n">
-        <v>706679.7628649013</v>
+        <v>713142.7539952545</v>
       </c>
       <c r="N6" t="n">
-        <v>805184.9189556639</v>
+        <v>811647.9100860187</v>
       </c>
       <c r="O6" t="n">
-        <v>550092.5415541268</v>
+        <v>556555.5326844821</v>
       </c>
       <c r="P6" t="n">
-        <v>808602.6492057103</v>
+        <v>815065.6403360652</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27106,13 +27106,13 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27560,7 +27560,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>249.5653734570881</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27578,7 +27578,7 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>249.5653734570881</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27603,25 +27603,25 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>249.3470173189561</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>371.8076126017833</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27679,7 +27679,7 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
         <v>134.2726973711268</v>
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.35838047348872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>159.6519859716246</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>88.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>26.1959257979226</v>
+        <v>258.9241762059412</v>
       </c>
       <c r="V6" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27843,7 +27843,7 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>347.6775194675577</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>379.1271237584759</v>
       </c>
       <c r="L7" t="n">
         <v>396.2015953708939</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>150.9483584875727</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28049,13 +28049,13 @@
         <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>326.808679808076</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>97.2736018156333</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28086,7 +28086,7 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>175.6474368353909</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>328.2037914052835</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28223,22 +28223,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28286,7 +28286,7 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>226.0367322273741</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>226.0367322273738</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28505,10 +28505,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>321</v>
@@ -28517,10 +28517,10 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28666,10 +28666,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S17" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
@@ -28706,10 +28706,10 @@
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28718,7 +28718,7 @@
         <v>321</v>
       </c>
       <c r="I18" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126235</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28760,13 +28760,13 @@
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28918,7 +28918,7 @@
         <v>321</v>
       </c>
       <c r="W20" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="X20" t="n">
         <v>321</v>
@@ -28946,7 +28946,7 @@
         <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="S21" t="n">
         <v>321</v>
@@ -28991,7 +28991,7 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -29000,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29104,13 +29104,13 @@
         <v>321</v>
       </c>
       <c r="F23" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G23" t="n">
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29174,16 +29174,16 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29414,7 +29414,7 @@
         <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -29423,13 +29423,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>18.05909831126235</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29948,10 +29948,10 @@
         <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -30058,10 +30058,10 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30119,19 +30119,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30182,10 +30182,10 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30222,7 +30222,7 @@
         <v>321</v>
       </c>
       <c r="J37" t="n">
-        <v>321.0000000000312</v>
+        <v>321</v>
       </c>
       <c r="K37" t="n">
         <v>321</v>
@@ -30356,16 +30356,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>321</v>
@@ -30416,7 +30416,7 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="W39" t="n">
         <v>321</v>
@@ -30425,7 +30425,7 @@
         <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>147.408184118027</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30596,13 +30596,13 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>18.05909831126201</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30650,7 +30650,7 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>321</v>
@@ -30678,7 +30678,7 @@
         <v>321</v>
       </c>
       <c r="D43" t="n">
-        <v>321</v>
+        <v>321.0000000000778</v>
       </c>
       <c r="E43" t="n">
         <v>321</v>
@@ -30830,19 +30830,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30878,10 +30878,10 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
@@ -30893,7 +30893,7 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="X45" t="n">
         <v>321</v>
@@ -34743,13 +34743,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34758,13 +34758,13 @@
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34889,25 +34889,25 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>4.487078903655562</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>349.5428277003017</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34934,19 +34934,19 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,25 +34983,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L5" t="n">
         <v>374</v>
       </c>
-      <c r="L5" t="n">
-        <v>64.70900502512563</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>306.7289592406477</v>
+      </c>
+      <c r="P5" t="n">
         <v>374</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58.67867865278593</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>235.5012052109774</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35129,7 +35129,7 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>102.8175810522572</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
         <v>172.8642181606765</v>
@@ -35138,10 +35138,10 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>111.9761860229066</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35183,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512562</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
+        <v>248.0502805878619</v>
+      </c>
+      <c r="N8" t="n">
         <v>374</v>
       </c>
-      <c r="N8" t="n">
-        <v>183.3412755627362</v>
-      </c>
       <c r="O8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35372,7 +35372,7 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>4.545391051338223</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>40.73843855582118</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,22 +35457,22 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>202.2390124881909</v>
+        <v>397.807439363043</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
         <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>341.8698541138008</v>
       </c>
       <c r="N14" t="n">
-        <v>165.9579345158108</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>649</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>179.5731479057565</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,13 +36168,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36411,16 +36411,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
+        <v>40.17514405185721</v>
+      </c>
+      <c r="N23" t="n">
         <v>649</v>
       </c>
-      <c r="N23" t="n">
-        <v>4.355038036034114</v>
-      </c>
       <c r="O23" t="n">
+        <v>162.757678164601</v>
+      </c>
+      <c r="P23" t="n">
         <v>649</v>
-      </c>
-      <c r="P23" t="n">
-        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
         <v>592.3686050224903</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36645,13 +36645,13 @@
         <v>648.9999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>218.2342914572864</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>236.2045428832663</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36879,16 +36879,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L29" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>59.83165132871924</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
         <v>175.9119195979899</v>
@@ -37122,10 +37122,10 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
+        <v>202.2390124881908</v>
+      </c>
+      <c r="N32" t="n">
         <v>649</v>
-      </c>
-      <c r="N32" t="n">
-        <v>40.17514405185732</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>649</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>649</v>
-      </c>
-      <c r="N35" t="n">
-        <v>60.29262328527629</v>
-      </c>
-      <c r="O35" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>342.3308260703577</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J37" t="n">
-        <v>329.5882314919923</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K37" t="n">
         <v>104.5500458709881</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
         <v>649</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37827,13 +37827,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
         <v>649</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37964,7 +37964,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>35.46378194444452</v>
+        <v>35.46378194452232</v>
       </c>
       <c r="E43" t="n">
         <v>40.01909516304346</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
         <v>175.9119195979899</v>
@@ -38070,16 +38070,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>490.5973598714331</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q44" t="n">
         <v>592.3686050224903</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
